--- a/artfynd/A 15915-2022 artfynd.xlsx
+++ b/artfynd/A 15915-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15915-2022 artfynd.xlsx
+++ b/artfynd/A 15915-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2109,7 +2109,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101621778</v>
+        <v>101628338</v>
       </c>
       <c r="B14" t="n">
         <v>90653</v>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2153,19 +2153,20 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen 20, Falun, Dlr</t>
+          <t>Lintjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549061.4417524863</v>
+        <v>549062.4133190202</v>
       </c>
       <c r="R14" t="n">
-        <v>6714584.476867552</v>
+        <v>6714585.473609536</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2194,7 +2195,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2204,7 +2205,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,12 +2225,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
+          <t>Bo karlstens, Lisa Olson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3591,7 +3597,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101628338</v>
+        <v>101621864</v>
       </c>
       <c r="B26" t="n">
         <v>90653</v>
@@ -3626,7 +3632,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3635,20 +3641,19 @@
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lintjärn, Dlr</t>
+          <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549062.4133190202</v>
+        <v>549073.3547397708</v>
       </c>
       <c r="R26" t="n">
-        <v>6714585.473609536</v>
+        <v>6714577.754263626</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3687,12 +3692,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar</t>
+          <t>3 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3707,22 +3712,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens, Lisa Olson, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101621864</v>
+        <v>101621386</v>
       </c>
       <c r="B27" t="n">
-        <v>90653</v>
+        <v>8377</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3735,21 +3740,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3757,22 +3762,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549073.3547397708</v>
+        <v>549088.1060991383</v>
       </c>
       <c r="R27" t="n">
-        <v>6714577.754263626</v>
+        <v>6714615.820611842</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3804,7 +3806,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3814,12 +3816,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,22 +3831,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101621386</v>
+        <v>101621616</v>
       </c>
       <c r="B28" t="n">
-        <v>8377</v>
+        <v>5113</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3862,21 +3859,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3893,10 +3890,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549088.1060991383</v>
+        <v>549112.193137274</v>
       </c>
       <c r="R28" t="n">
-        <v>6714615.820611842</v>
+        <v>6714583.200575075</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3928,7 +3925,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3938,7 +3935,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3965,10 +3962,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101621616</v>
+        <v>101621847</v>
       </c>
       <c r="B29" t="n">
-        <v>5113</v>
+        <v>90653</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3981,21 +3978,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4003,19 +4000,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549112.193137274</v>
+        <v>549077.1740905737</v>
       </c>
       <c r="R29" t="n">
-        <v>6714583.200575075</v>
+        <v>6714586.657968335</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4084,7 +4084,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101621847</v>
+        <v>101621714</v>
       </c>
       <c r="B30" t="n">
         <v>90653</v>
@@ -4122,11 +4122,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4134,10 +4129,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549077.1740905737</v>
+        <v>549112.193137274</v>
       </c>
       <c r="R30" t="n">
-        <v>6714586.657968335</v>
+        <v>6714583.200575075</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4169,7 +4164,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4179,7 +4174,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4206,10 +4201,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101621714</v>
+        <v>101621566</v>
       </c>
       <c r="B31" t="n">
-        <v>90653</v>
+        <v>4711</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4222,21 +4217,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4245,16 +4240,18 @@
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549112.193137274</v>
+        <v>549086.4172885313</v>
       </c>
       <c r="R31" t="n">
-        <v>6714583.200575075</v>
+        <v>6714595.143712222</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4286,7 +4283,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4296,7 +4293,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4323,10 +4320,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101621566</v>
+        <v>101722286</v>
       </c>
       <c r="B32" t="n">
-        <v>4711</v>
+        <v>5113</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4339,41 +4336,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen 20, Falun, Dlr</t>
+          <t>Lintjärn norra, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549086.4172885313</v>
+        <v>549113.1081232589</v>
       </c>
       <c r="R32" t="n">
-        <v>6714595.143712222</v>
+        <v>6714624.520889821</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4405,7 +4404,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4415,7 +4414,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4424,28 +4423,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101722286</v>
+        <v>101622470</v>
       </c>
       <c r="B33" t="n">
-        <v>5113</v>
+        <v>5135</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4458,43 +4458,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lintjärn norra, Falun, Dlr</t>
+          <t>Lintjärn, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549113.1081232589</v>
+        <v>549139.6207582084</v>
       </c>
       <c r="R33" t="n">
-        <v>6714624.520889821</v>
+        <v>6714558.494177476</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4526,7 +4522,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4536,7 +4532,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,128 +4553,10 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>101622470</v>
-      </c>
-      <c r="B34" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Lintjärn, Falun, Dlr</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>549139.6207582084</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6714558.494177476</v>
-      </c>
-      <c r="S34" t="n">
-        <v>25</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Vika</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Cecilia Rastad</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Cecilia Rastad, Lisa Olson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15915-2022 artfynd.xlsx
+++ b/artfynd/A 15915-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101289212</v>
+        <v>101289361</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lintjärnsvägen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549173.2730817648</v>
+        <v>549253</v>
       </c>
       <c r="R2" t="n">
-        <v>6714583.049332491</v>
+        <v>6714588</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,65 +783,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101288547</v>
+        <v>101621714</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549080.8167712033</v>
+        <v>549112</v>
       </c>
       <c r="R3" t="n">
-        <v>6714644.735033872</v>
+        <v>6714584</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,22 +853,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,73 +883,67 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101288824</v>
+        <v>101621778</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549122.1801201423</v>
+        <v>549061</v>
       </c>
       <c r="R4" t="n">
-        <v>6714609.399933633</v>
+        <v>6714585</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,22 +970,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,69 +1000,67 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101288488</v>
+        <v>101621800</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549070.2275123987</v>
+        <v>549059</v>
       </c>
       <c r="R5" t="n">
-        <v>6714662.785806493</v>
+        <v>6714596</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,22 +1087,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,72 +1117,68 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101289309</v>
+        <v>101621838</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549225.4348628737</v>
+        <v>549064</v>
       </c>
       <c r="R6" t="n">
-        <v>6714586.711494131</v>
+        <v>6714587</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,22 +1205,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,70 +1234,74 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101288286</v>
+        <v>101621847</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549081.7013288904</v>
+        <v>549077</v>
       </c>
       <c r="R7" t="n">
-        <v>6714652.123381944</v>
+        <v>6714587</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,27 +1328,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>12 vinterståndare, 100-tal bladrosetter</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,64 +1358,67 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101289157</v>
+        <v>101621864</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549155.7451236016</v>
+        <v>549073</v>
       </c>
       <c r="R8" t="n">
-        <v>6714568.057461721</v>
+        <v>6714578</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1471,27 +1445,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>12 vinterståndare, 100-tal bladrosetter</t>
+          <t>3 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,27 +1480,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101289361</v>
+        <v>101625897</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,38 +1503,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549253.4923193179</v>
+        <v>549319</v>
       </c>
       <c r="R9" t="n">
-        <v>6714588.078087876</v>
+        <v>6714622</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,22 +1568,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:07</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:07</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,82 +1582,78 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101289275</v>
+        <v>101628338</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549200.3590500643</v>
+        <v>549062</v>
       </c>
       <c r="R10" t="n">
-        <v>6714583.41874067</v>
+        <v>6714586</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1712,22 +1677,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:03</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:03</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,64 +1702,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens, Cecilia Rastad, Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101288221</v>
+        <v>101629323</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen 20, Falun, Dlr</t>
+          <t>Lintjärn norra, Lintjärnsvägen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549115.7415159175</v>
+        <v>549275</v>
       </c>
       <c r="R11" t="n">
-        <v>6714648.161029706</v>
+        <v>6714582</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1826,22 +1790,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,70 +1814,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101288844</v>
+        <v>101622498</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen, Falun, Dlr</t>
+          <t>Sjökanten, Lintjärn, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549145.1619676381</v>
+        <v>549135</v>
       </c>
       <c r="R12" t="n">
-        <v>6714585.61673612</v>
+        <v>6714548</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1940,22 +1906,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,27 +1936,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cecilia Rastad, Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101626340</v>
+        <v>101621566</v>
       </c>
       <c r="B13" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,29 +1976,27 @@
           <t>(Kraatz, 1881)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lintjärn, Dlr</t>
+          <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>549091.3899589492</v>
+        <v>549086</v>
       </c>
       <c r="R13" t="n">
-        <v>6714664.057317874</v>
+        <v>6714595</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2066,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2076,12 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På torrgran död sedan minst 5-10 år</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,34 +2044,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101628338</v>
+        <v>101626340</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,34 +2073,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2160,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>549062.4133190202</v>
+        <v>549092</v>
       </c>
       <c r="R14" t="n">
-        <v>6714585.473609536</v>
+        <v>6714664</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2193,24 +2139,14 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gamla fruktkroppar</t>
+          <t>På torrgran död sedan minst 5-10 år</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,6 +2155,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2230,22 +2167,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens, Lisa Olson, Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101621215</v>
+        <v>101288488</v>
       </c>
       <c r="B15" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,21 +2185,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2275,7 +2207,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2284,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549133.5371759173</v>
+        <v>549070</v>
       </c>
       <c r="R15" t="n">
-        <v>6714643.485886835</v>
+        <v>6714663</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2314,22 +2246,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,27 +2276,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101627823</v>
+        <v>101621616</v>
       </c>
       <c r="B16" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,29 +2316,27 @@
           <t>Paykull, 1800</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lintjärn, Dlr</t>
+          <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549109.9122986946</v>
+        <v>549112</v>
       </c>
       <c r="R16" t="n">
-        <v>6714642.180591786</v>
+        <v>6714584</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2440,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2450,12 +2375,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På torrgran död sedan minst 5-10 år</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,27 +2390,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Lisa Olson, Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101629199</v>
+        <v>101627823</v>
       </c>
       <c r="B17" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,40 +2413,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lintjärn norra, Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärn, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549315.2613552373</v>
+        <v>549110</v>
       </c>
       <c r="R17" t="n">
-        <v>6714609.576178946</v>
+        <v>6714642</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2558,24 +2479,14 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gnag synligt högre upp på torrakan.</t>
+          <t>På torrgran död sedan minst 5-10 år</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,27 +2501,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens, Lisa Olson, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101629323</v>
+        <v>101722286</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2618,45 +2524,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lintjärn norra, Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärn norra, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549275.2416777718</v>
+        <v>549113</v>
       </c>
       <c r="R18" t="n">
-        <v>6714582.474021117</v>
+        <v>6714625</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2688,7 +2592,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2698,7 +2602,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,15 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101621286</v>
+        <v>101622470</v>
       </c>
       <c r="B19" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2742,37 +2641,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen 20, Falun, Dlr</t>
+          <t>Lintjärn, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549111.7884191386</v>
+        <v>549140</v>
       </c>
       <c r="R19" t="n">
-        <v>6714649.09070293</v>
+        <v>6714559</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2804,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2814,12 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gnag synligt med kikare högre upp på stammen.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2828,6 +2724,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2839,44 +2736,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101622498</v>
+        <v>101621215</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2884,20 +2776,19 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sjökanten, Lintjärn, Falun, Dlr</t>
+          <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549134.8299728279</v>
+        <v>549134</v>
       </c>
       <c r="R20" t="n">
-        <v>6714548.593563315</v>
+        <v>6714644</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2929,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2939,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2959,22 +2850,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson</t>
+          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101629142</v>
+        <v>101621286</v>
       </c>
       <c r="B21" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3000,25 +2886,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lintjärn norra, Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549319.2952355813</v>
+        <v>549112</v>
       </c>
       <c r="R21" t="n">
-        <v>6714602.746690443</v>
+        <v>6714650</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3050,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3060,7 +2940,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gnag synligt med kikare högre upp på stammen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3069,7 +2954,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3081,73 +2965,59 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101629607</v>
+        <v>101621386</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lintjärn norra, Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549194.4359711399</v>
+        <v>549088</v>
       </c>
       <c r="R22" t="n">
-        <v>6714584.321468701</v>
+        <v>6714616</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3179,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3189,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3198,34 +3068,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101621838</v>
+        <v>101626009</v>
       </c>
       <c r="B23" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3233,48 +3097,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen 20, Falun, Dlr</t>
+          <t>Lintjärn, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549064.369828287</v>
+        <v>549328</v>
       </c>
       <c r="R23" t="n">
-        <v>6714586.483750966</v>
+        <v>6714611</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3301,24 +3163,14 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>9 fruktkroppar.</t>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3334,27 +3186,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101621800</v>
+        <v>101629142</v>
       </c>
       <c r="B24" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3362,44 +3209,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen 20, Falun, Dlr</t>
+          <t>Lintjärn norra, Lintjärnsvägen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549059.3046591203</v>
+        <v>549319</v>
       </c>
       <c r="R24" t="n">
-        <v>6714596.741839673</v>
+        <v>6714603</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3431,7 +3277,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3441,7 +3287,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3450,6 +3296,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3461,73 +3308,55 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101629688</v>
+        <v>101629199</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lintjärn norra,  Lintjärnsvägen, Falun, Dlr</t>
+          <t>Lintjärn norra, Lintjärnsvägen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549173.1792293122</v>
+        <v>549315</v>
       </c>
       <c r="R25" t="n">
-        <v>6714589.932731962</v>
+        <v>6714610</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3559,7 +3388,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,7 +3398,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gnag synligt högre upp på torrakan.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3578,7 +3412,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3597,60 +3430,47 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101621864</v>
+        <v>101288221</v>
       </c>
       <c r="B26" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549073.3547397708</v>
+        <v>549116</v>
       </c>
       <c r="R26" t="n">
-        <v>6714577.754263626</v>
+        <v>6714649</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3677,27 +3497,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3712,69 +3527,59 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Bo karlstens, Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101621386</v>
+        <v>101288286</v>
       </c>
       <c r="B27" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549088.1060991383</v>
+        <v>549081</v>
       </c>
       <c r="R27" t="n">
-        <v>6714615.820611842</v>
+        <v>6714652</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3801,22 +3606,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>12 vinterståndare, 100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3831,69 +3641,72 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101621616</v>
+        <v>101288547</v>
       </c>
       <c r="B28" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549112.193137274</v>
+        <v>549080</v>
       </c>
       <c r="R28" t="n">
-        <v>6714583.200575075</v>
+        <v>6714645</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3920,22 +3733,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3950,72 +3763,68 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101621847</v>
+        <v>101288824</v>
       </c>
       <c r="B29" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lintjärnsvägen 20, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549077.1740905737</v>
+        <v>549122</v>
       </c>
       <c r="R29" t="n">
-        <v>6714586.657968335</v>
+        <v>6714609</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4042,22 +3851,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4072,67 +3881,59 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101621714</v>
+        <v>101288844</v>
       </c>
       <c r="B30" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen 20, Falun, Dlr</t>
+          <t>Lintjärnsvägen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549112.193137274</v>
+        <v>549145</v>
       </c>
       <c r="R30" t="n">
-        <v>6714583.200575075</v>
+        <v>6714586</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4159,22 +3960,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4189,69 +3990,59 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101621566</v>
+        <v>101289157</v>
       </c>
       <c r="B31" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lintjärnsvägen 20, Falun, Dlr</t>
+          <t>Lintjärnsvägen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549086.4172885313</v>
+        <v>549155</v>
       </c>
       <c r="R31" t="n">
-        <v>6714595.143712222</v>
+        <v>6714568</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4278,22 +4069,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>12 vinterståndare, 100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4308,71 +4104,59 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101722286</v>
+        <v>101289212</v>
       </c>
       <c r="B32" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lintjärn norra, Falun, Dlr</t>
+          <t>Lintjärnsvägen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549113.1081232589</v>
+        <v>549174</v>
       </c>
       <c r="R32" t="n">
-        <v>6714624.520889821</v>
+        <v>6714583</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4399,22 +4183,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4423,74 +4207,74 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101622470</v>
+        <v>101289275</v>
       </c>
       <c r="B33" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lintjärn, Falun, Dlr</t>
+          <t>Lintjärnsvägen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549139.6207582084</v>
+        <v>549200</v>
       </c>
       <c r="R33" t="n">
-        <v>6714558.494177476</v>
+        <v>6714583</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4517,22 +4301,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4541,22 +4325,496 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>101289309</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lintjärnsvägen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>549225</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6714586</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-05-30</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-05-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>101625930</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lintjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>549341</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6714612</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>101629607</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lintjärn norra, Lintjärnsvägen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>549194</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6714584</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
           <t>Cecilia Rastad</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Cecilia Rastad, Lisa Olson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>101629688</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lintjärn norra,  Lintjärnsvägen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>549174</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6714590</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15915-2022 artfynd.xlsx
+++ b/artfynd/A 15915-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101289361</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621714</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621778</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621800</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621838</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621847</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621864</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101625897</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1711,6 +1756,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101628338</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1830,6 +1880,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101629323</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1945,6 +2000,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101622498</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2059,6 +2119,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621566</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2171,6 +2236,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101626340</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2285,6 +2355,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101288488</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2399,6 +2474,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621616</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2510,6 +2590,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101627823</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2627,6 +2712,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101722286</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2740,6 +2830,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101622470</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2854,6 +2949,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621215</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2969,6 +3069,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621286</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3083,6 +3188,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621386</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3195,6 +3305,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101626009</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3312,6 +3427,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101629142</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3427,6 +3547,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101629199</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3536,6 +3661,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101288221</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3650,6 +3780,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101288286</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3772,6 +3907,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101288547</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3890,6 +4030,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101288824</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3999,6 +4144,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101288844</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4113,6 +4263,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101289157</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4222,6 +4377,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101289212</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4340,6 +4500,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101289275</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4457,6 +4622,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101289309</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4567,6 +4737,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101625930</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4691,6 +4866,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101629607</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4815,8 +4995,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101629688</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>